--- a/замер скорости.xlsx
+++ b/замер скорости.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\работа Модуль\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Egenie\STM32CubeIDE\workspace_1.17.0\Eth_Module\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16800" windowHeight="6924"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16800" windowHeight="7125"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="97">
   <si>
     <t>скорость</t>
   </si>
@@ -210,6 +210,111 @@
   </si>
   <si>
     <t>12.42 КБ/с</t>
+  </si>
+  <si>
+    <t>Устойчивая нагрузка (FDCAN1 &lt;-&gt; FDCAN2)</t>
+  </si>
+  <si>
+    <t>============================================================</t>
+  </si>
+  <si>
+    <t>ПРОВЕРКА УСТОЙЧИВОЙ НАГРУЗКИ (count=300, 180 с)</t>
+  </si>
+  <si>
+    <t>192.168.0.18:2001 -&gt; 192.168.0.18:2002  устойчивая нагрузка 180.0 с, пачками по 300 кадров, 1000 Kbit/s</t>
+  </si>
+  <si>
+    <t>Время: 180.0247 с</t>
+  </si>
+  <si>
+    <t>Скорость: 4979.3 пакет/с, 38.90 КБ/с</t>
+  </si>
+  <si>
+    <t>Доставлено: 896400 (суммарно)</t>
+  </si>
+  <si>
+    <t>Все кадры дошли и совпадают побайтово -- OK</t>
+  </si>
+  <si>
+    <t>########## count = 310 ##########</t>
+  </si>
+  <si>
+    <t>192.168.0.18:2001 -&gt; 192.168.0.18:2002  310 кадров, 1000 Kbit/s</t>
+  </si>
+  <si>
+    <t>Время: 0.0585 с</t>
+  </si>
+  <si>
+    <t>Скорость: 5296.5 пакет/с, 41.38 КБ/с</t>
+  </si>
+  <si>
+    <t>Доставлено: 310 из 310</t>
+  </si>
+  <si>
+    <t>########## count = 320 ##########</t>
+  </si>
+  <si>
+    <t>192.168.0.18:2001 -&gt; 192.168.0.18:2002  320 кадров, 1000 Kbit/s</t>
+  </si>
+  <si>
+    <t>Скорость: 5471.0 пакет/с, 42.74 КБ/с</t>
+  </si>
+  <si>
+    <t>Доставлено: 320 из 320</t>
+  </si>
+  <si>
+    <t>########## count = 330 ##########</t>
+  </si>
+  <si>
+    <t>192.168.0.18:2001 -&gt; 192.168.0.18:2002  330 кадров, 1000 Kbit/s</t>
+  </si>
+  <si>
+    <t>Время: 10.0016 с</t>
+  </si>
+  <si>
+    <t>Скорость: 31.4 пакет/с, 0.25 КБ/с</t>
+  </si>
+  <si>
+    <t>Доставлено: 314 из 330</t>
+  </si>
+  <si>
+    <t>&lt;Error&gt; Часть кадров потеряна или данные не совпадают</t>
+  </si>
+  <si>
+    <t>&lt;Стоп&gt; Потери начались на count=330, дальше не идём</t>
+  </si>
+  <si>
+    <t>ИТОГ (поиск максимума, 1000 Kbit/s)</t>
+  </si>
+  <si>
+    <t>count=  300     4063.2 пакет/с      31.74 КБ/с   300/300   OK</t>
+  </si>
+  <si>
+    <t>count=  310     5296.5 пакет/с      41.38 КБ/с   310/310   OK</t>
+  </si>
+  <si>
+    <t>count=  320     5471.0 пакет/с      42.74 КБ/с   320/320   OK</t>
+  </si>
+  <si>
+    <t>count=  330       31.4 пакет/с       0.25 КБ/с   314/330   ОШИБКА</t>
+  </si>
+  <si>
+    <t>Практический максимум без потерь: count=320 (~5471 пакет/с на 1000 Kbit/s)</t>
+  </si>
+  <si>
+    <t>ПРОВЕРКА УСТОЙЧИВОЙ НАГРУЗКИ (count=320, 180 с)</t>
+  </si>
+  <si>
+    <t>192.168.0.18:2001 -&gt; 192.168.0.18:2002  устойчивая нагрузка 180.0 с, пачками по 320 кадров, 1000 Kbit/s</t>
+  </si>
+  <si>
+    <t>&lt;Error&gt; Пачка потеряна/не совпала (принято 314 из 320) -- прерываю устойчивый прогон</t>
+  </si>
+  <si>
+    <t>Время: 10.0011 с</t>
+  </si>
+  <si>
+    <t>Доставлено: 314 (суммарно)</t>
   </si>
 </sst>
 </file>
@@ -272,10 +377,10 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -556,42 +661,42 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:J75"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="12.5546875" customWidth="1"/>
-    <col min="2" max="2" width="14.44140625" customWidth="1"/>
+    <col min="1" max="1" width="12.53125" customWidth="1"/>
+    <col min="2" max="2" width="14.46484375" customWidth="1"/>
     <col min="3" max="3" width="17.6640625" customWidth="1"/>
     <col min="4" max="4" width="11.6640625" customWidth="1"/>
-    <col min="7" max="7" width="12.88671875" customWidth="1"/>
+    <col min="7" max="7" width="12.86328125" customWidth="1"/>
     <col min="8" max="8" width="14.6640625" customWidth="1"/>
-    <col min="9" max="9" width="11.77734375" customWidth="1"/>
+    <col min="9" max="9" width="11.796875" customWidth="1"/>
     <col min="10" max="10" width="13.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="G1" s="2" t="s">
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="G1" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-    </row>
-    <row r="2" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+    </row>
+    <row r="2" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -617,7 +722,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -643,7 +748,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -669,7 +774,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -695,7 +800,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -721,15 +826,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="3" t="s">
+    <row r="9" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A9" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="G9" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
         <v>0</v>
       </c>
@@ -755,7 +860,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>5</v>
       </c>
@@ -781,7 +886,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>6</v>
       </c>
@@ -807,7 +912,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>7</v>
       </c>
@@ -833,7 +938,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>8</v>
       </c>
@@ -859,15 +964,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="3" t="s">
+    <row r="16" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A16" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="G16" s="3" t="s">
+      <c r="G16" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A17" s="1" t="s">
         <v>0</v>
       </c>
@@ -893,7 +998,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>5</v>
       </c>
@@ -919,7 +1024,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>6</v>
       </c>
@@ -945,7 +1050,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>7</v>
       </c>
@@ -971,7 +1076,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>8</v>
       </c>
@@ -997,10 +1102,239 @@
         <v>30</v>
       </c>
     </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A24" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A25" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A26" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A27" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A28" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A29" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A30" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A31" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A32" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A35" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A36" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A37" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A38" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A39" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A40" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A42" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A43" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A44" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A45" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A46" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A47" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A49" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A50" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A51" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A52" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A53" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A54" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A56" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A57" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A58" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A59" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A60" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A61" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A62" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A63" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A65" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A67" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A68" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A69" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A70" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A71" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A72" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A73" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A74" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A75" t="s">
+        <v>84</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="G1:J1"/>
+    <mergeCell ref="A24:D24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
